--- a/docs/Requisitos_Sistema.xlsx
+++ b/docs/Requisitos_Sistema.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>El sistema debe permitir al usuario buscar productos mediante un buscador.</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
   </si>
   <si>
     <t>RF-08</t>
@@ -212,27 +209,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -256,25 +239,25 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" quotePrefix="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -354,10 +337,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;#xFF2D;&amp;amp;#xFF33; &amp;amp;#xFF30;&amp;amp;#x30B4;&amp;amp;#x30B7;&amp;amp;#x30C3;&amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;#xB9D1;&amp;amp;#xC740; &amp;amp;#xACE0;&amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;#x5B8B;&amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;#x65B0;&amp;amp;#x7D30;&amp;amp;#x660E;&amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -388,10 +371,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;#xFF2D;&amp;amp;#xFF33; &amp;amp;#xFF30;&amp;amp;#x30B4;&amp;amp;#x30B7;&amp;amp;#x30C3;&amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;#xB9D1;&amp;amp;#xC740; &amp;amp;#xACE0;&amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;#x5B8B;&amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;#x65B0;&amp;amp;#x7D30;&amp;amp;#x660E;&amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -592,7 +575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A142B59B-71ED-42EC-B90C-CBF0BE3DC7D4}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DA0518A0-1F7D-4AE0-B4B6-6A5A143F2499}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -719,15 +702,15 @@
         <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -741,10 +724,10 @@
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
@@ -758,10 +741,10 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
@@ -775,16 +758,16 @@
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>9</v>
@@ -792,10 +775,10 @@
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
@@ -809,10 +792,10 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
@@ -826,53 +809,53 @@
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +866,7 @@
   </autoFilter>
   <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
